--- a/data/trans_orig/IP07C03-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07C03-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5084</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>13585</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11344</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9817</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17589</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>17081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27004</t>
+          <t>26897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,03%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25977</t>
+          <t>26460</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35467</t>
+          <t>35991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>28538</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39027</t>
+          <t>39985</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56866</t>
+          <t>57057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72472</t>
+          <t>71766</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>72,62%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5823</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14738</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>13208</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25413</t>
+          <t>24509</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22384</t>
+          <t>22596</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37112</t>
+          <t>37174</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8953</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>14079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22557</t>
+          <t>22815</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15427</t>
+          <t>15352</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23769</t>
+          <t>24218</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35584</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,91%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15993</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7706</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>14907</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17084</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28808</t>
+          <t>28429</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>52,63%</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4337</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17163</t>
+          <t>17472</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20899</t>
+          <t>21132</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>23033</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35418</t>
+          <t>35655</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,53%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11032</t>
+          <t>11132</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8696</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18039</t>
+          <t>17715</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>22034</t>
+          <t>22292</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>35250</t>
+          <t>35032</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2651</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15059</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10282</t>
+          <t>10552</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18050</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20358</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30986</t>
+          <t>31150</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,66%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>10118</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>11283</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9181</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19180</t>
+          <t>18729</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>17570</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19882</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>22836</t>
+          <t>23451</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34651</t>
+          <t>34714</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,13%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6529</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14598</t>
+          <t>14535</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7913</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>16436</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16614</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28393</t>
+          <t>28050</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>52,63%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>21580</t>
+          <t>22127</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>33297</t>
+          <t>32664</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>22355</t>
+          <t>21996</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>33585</t>
+          <t>33568</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>46364</t>
+          <t>47049</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>62764</t>
+          <t>64062</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>13331</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>25086</t>
+          <t>24775</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>18391</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>29575</t>
+          <t>29743</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>35522</t>
+          <t>33752</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>51978</t>
+          <t>51253</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>25087</t>
+          <t>25129</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>39464</t>
+          <t>38708</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>26840</t>
+          <t>26451</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>39920</t>
+          <t>39160</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>54455</t>
+          <t>55362</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>74686</t>
+          <t>74926</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,93%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>31564</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>45966</t>
+          <t>46111</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>27242</t>
+          <t>27730</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>40542</t>
+          <t>40311</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>63795</t>
+          <t>63626</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>83212</t>
+          <t>82758</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,36%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>136044</t>
+          <t>134971</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>163485</t>
+          <t>162810</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>144211</t>
+          <t>144813</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>172413</t>
+          <t>172218</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>288252</t>
+          <t>289017</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>326861</t>
+          <t>327604</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,62%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>107415</t>
+          <t>107607</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>132846</t>
+          <t>134436</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>119161</t>
+          <t>120443</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>148132</t>
+          <t>148098</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>235800</t>
+          <t>235121</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>273946</t>
+          <t>274062</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>23550</t>
+          <t>24387</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>22027</t>
+          <t>21453</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>38783</t>
+          <t>38337</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>14563</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12358</t>
+          <t>12681</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21864</t>
+          <t>21573</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22295</t>
+          <t>22276</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34451</t>
+          <t>35017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14224</t>
+          <t>13813</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>16351</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15951</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27817</t>
+          <t>27580</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>550</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>866</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24395</t>
+          <t>23926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35287</t>
+          <t>35026</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35658</t>
+          <t>35323</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45824</t>
+          <t>45127</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63437</t>
+          <t>63851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78420</t>
+          <t>78821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,69%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>10795</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21088</t>
+          <t>21156</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15824</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18465</t>
+          <t>17939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32921</t>
+          <t>32978</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13751</t>
+          <t>13797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18502</t>
+          <t>18307</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17163</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29086</t>
+          <t>29178</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,42%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9477</t>
+          <t>9431</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17234</t>
+          <t>17211</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11502</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20479</t>
+          <t>20172</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23403</t>
+          <t>23712</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35675</t>
+          <t>36108</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17652</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10949</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20918</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21014</t>
+          <t>21396</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34668</t>
+          <t>34978</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15108</t>
+          <t>15289</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25237</t>
+          <t>25930</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>27791</t>
+          <t>28178</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41523</t>
+          <t>42379</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>58,08%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14328</t>
+          <t>14568</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3699</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9656</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9175</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16701</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16548</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21609</t>
+          <t>21744</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31876</t>
+          <t>31587</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,48%</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>19716</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>20090</t>
+          <t>19764</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26991</t>
+          <t>26984</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10780</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>19402</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>33447</t>
+          <t>33560</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>44422</t>
+          <t>44609</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,55%</t>
         </is>
       </c>
     </row>
@@ -10782,7 +10782,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>12523</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>23980</t>
+          <t>23897</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>17421</t>
+          <t>17621</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>29362</t>
+          <t>29573</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>32897</t>
+          <t>32372</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>49091</t>
+          <t>48658</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>23140</t>
+          <t>23039</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>35500</t>
+          <t>35073</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>21856</t>
+          <t>21132</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>33495</t>
+          <t>32861</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>47799</t>
+          <t>48722</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>64546</t>
+          <t>65375</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,86%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>11922</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>14452</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>27052</t>
+          <t>27811</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>19106</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>31792</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>36584</t>
+          <t>36722</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>56170</t>
+          <t>55677</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>48018</t>
+          <t>48046</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>61549</t>
+          <t>60791</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>40320</t>
+          <t>39807</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>54053</t>
+          <t>53768</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>91126</t>
+          <t>92338</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>111792</t>
+          <t>111213</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,36%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12259,7 +12259,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>98087</t>
+          <t>97841</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>124966</t>
+          <t>124482</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>135170</t>
+          <t>135433</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>165059</t>
+          <t>163032</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>240732</t>
+          <t>242737</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>284972</t>
+          <t>283460</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>165690</t>
+          <t>166414</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>194474</t>
+          <t>194426</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>141861</t>
+          <t>143213</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>170151</t>
+          <t>171316</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>314991</t>
+          <t>316568</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>358204</t>
+          <t>357780</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>21644</t>
+          <t>20886</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>22352</t>
+          <t>22909</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>21048</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38520</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>12120</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10632</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22018</t>
+          <t>21917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19037</t>
+          <t>18860</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11611</t>
+          <t>11818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20436</t>
+          <t>20390</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25228</t>
+          <t>24728</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37211</t>
+          <t>37092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>740</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>6358</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14002,12 +14002,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>572</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14017,12 +14017,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32706</t>
+          <t>32889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43327</t>
+          <t>43561</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40950</t>
+          <t>40794</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50359</t>
+          <t>50809</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77829</t>
+          <t>77213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92179</t>
+          <t>91267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17294</t>
+          <t>17850</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14711</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14258</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28381</t>
+          <t>28902</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>17227</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27394</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16509</t>
+          <t>15963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25525</t>
+          <t>25564</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36598</t>
+          <t>36621</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50736</t>
+          <t>51005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6801</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>16853</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27215</t>
+          <t>27117</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>708</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -15223,7 +15223,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15238,7 +15238,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -15301,7 +15301,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15316,7 +15316,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15386,7 +15386,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17093</t>
+          <t>17061</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26005</t>
+          <t>26048</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22090</t>
+          <t>22282</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31263</t>
+          <t>30726</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41284</t>
+          <t>41779</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54542</t>
+          <t>54603</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14066</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23384</t>
+          <t>22948</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>709</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6396</t>
+          <t>6854</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18827</t>
+          <t>18553</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,52%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>18293</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>29827</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,76%</t>
         </is>
       </c>
     </row>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>12163</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15505</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24375</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21526</t>
+          <t>21648</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>28201</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>40174</t>
+          <t>39503</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>51454</t>
+          <t>51523</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,91%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>14068</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>19956</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -17156,7 +17156,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17191,7 +17191,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20131</t>
+          <t>20526</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>33211</t>
+          <t>34884</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24139</t>
+          <t>23807</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>37337</t>
+          <t>36712</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>47199</t>
+          <t>46833</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>66232</t>
+          <t>66091</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>29847</t>
+          <t>28664</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>42919</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>23561</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>36930</t>
+          <t>36640</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>57564</t>
+          <t>56837</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>76687</t>
+          <t>76906</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,17%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>724</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>12432</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17951,7 +17951,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>24060</t>
+          <t>23980</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>37966</t>
+          <t>38464</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>22737</t>
+          <t>22266</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>36446</t>
+          <t>35688</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>50320</t>
+          <t>49242</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>70435</t>
+          <t>69029</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,0%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>34312</t>
+          <t>34670</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>49031</t>
+          <t>48591</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>36324</t>
+          <t>36470</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>50244</t>
+          <t>50518</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>74840</t>
+          <t>76257</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>95674</t>
+          <t>96828</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,72%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>11949</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>17278</t>
+          <t>17058</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>160790</t>
+          <t>160778</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>190672</t>
+          <t>191182</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18956,7 +18956,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>178840</t>
+          <t>179384</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>208334</t>
+          <t>209728</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>350503</t>
+          <t>348197</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>393340</t>
+          <t>392057</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>128979</t>
+          <t>130300</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>159386</t>
+          <t>161745</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>119224</t>
+          <t>118549</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>149101</t>
+          <t>147671</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>257244</t>
+          <t>256623</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>299951</t>
+          <t>299379</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>13006</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>28004</t>
+          <t>26796</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>12185</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>25155</t>
+          <t>25884</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>28854</t>
+          <t>28997</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>49594</t>
+          <t>48397</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,47 +19325,47 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>6162</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>11596</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
           <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>6162</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="inlineStr">
-        <is>
-          <t>2910</t>
-        </is>
-      </c>
-      <c r="T55" s="2" t="inlineStr">
-        <is>
-          <t>11248</t>
-        </is>
-      </c>
-      <c r="U55" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="W55" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19393,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,12 +19473,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
